--- a/artfynd/Herrbergsliden norr artfynd.xlsx
+++ b/artfynd/Herrbergsliden norr artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>122745425</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>122745423</v>
       </c>
       <c r="B9" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>122745424</v>
       </c>
       <c r="B10" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>122745438</v>
       </c>
       <c r="B11" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>122745445</v>
       </c>
       <c r="B12" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>122745426</v>
       </c>
       <c r="B19" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>122745439</v>
       </c>
       <c r="B20" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>122745446</v>
       </c>
       <c r="B21" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>122745451</v>
       </c>
       <c r="B22" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>122745453</v>
       </c>
       <c r="B23" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>122745457</v>
       </c>
       <c r="B24" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>122745444</v>
       </c>
       <c r="B28" t="n">
-        <v>91924</v>
+        <v>91985</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>122745447</v>
       </c>
       <c r="B29" t="n">
-        <v>91924</v>
+        <v>91985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>122745452</v>
       </c>
       <c r="B30" t="n">
-        <v>91924</v>
+        <v>91985</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>122745448</v>
       </c>
       <c r="B35" t="n">
-        <v>91876</v>
+        <v>91937</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>122745421</v>
       </c>
       <c r="B45" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>122745454</v>
       </c>
       <c r="B46" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>122745456</v>
       </c>
       <c r="B47" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>122745455</v>
       </c>
       <c r="B48" t="n">
-        <v>80463</v>
+        <v>80493</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>122745458</v>
       </c>
       <c r="B49" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>122745422</v>
       </c>
       <c r="B50" t="n">
-        <v>80394</v>
+        <v>80438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>122745449</v>
       </c>
       <c r="B51" t="n">
-        <v>80394</v>
+        <v>80438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>122745428</v>
       </c>
       <c r="B52" t="n">
-        <v>92127</v>
+        <v>92593</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>122745464</v>
       </c>
       <c r="B53" t="n">
-        <v>92127</v>
+        <v>92593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>122745465</v>
       </c>
       <c r="B54" t="n">
-        <v>92127</v>
+        <v>92593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>122745468</v>
       </c>
       <c r="B55" t="n">
-        <v>92127</v>
+        <v>92593</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>122745427</v>
       </c>
       <c r="B64" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>122745429</v>
       </c>
       <c r="B65" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>122745460</v>
       </c>
       <c r="B66" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>122745462</v>
       </c>
       <c r="B67" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>122745463</v>
       </c>
       <c r="B92" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>122745467</v>
       </c>
       <c r="B93" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>122745433</v>
       </c>
       <c r="B95" t="n">
-        <v>91924</v>
+        <v>91985</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>122745432</v>
       </c>
       <c r="B100" t="n">
-        <v>92373</v>
+        <v>92406</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>122745461</v>
       </c>
       <c r="B101" t="n">
-        <v>92373</v>
+        <v>92406</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>122745466</v>
       </c>
       <c r="B105" t="n">
-        <v>91876</v>
+        <v>91937</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>122745430</v>
       </c>
       <c r="B127" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>122745459</v>
       </c>
       <c r="B128" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>122745431</v>
       </c>
       <c r="B135" t="n">
-        <v>80394</v>
+        <v>80438</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>122745435</v>
       </c>
       <c r="B140" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>122745442</v>
       </c>
       <c r="B142" t="n">
-        <v>91909</v>
+        <v>91970</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>122745475</v>
       </c>
       <c r="B149" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>122745470</v>
       </c>
       <c r="B151" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>122745472</v>
       </c>
       <c r="B152" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>122745477</v>
       </c>
       <c r="B153" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>122745473</v>
       </c>
       <c r="B156" t="n">
-        <v>92373</v>
+        <v>92406</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>122745476</v>
       </c>
       <c r="B161" t="n">
-        <v>80463</v>
+        <v>80493</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
